--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/93.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/93.xlsx
@@ -426,13 +426,13 @@
         <v>-7.220750903175348</v>
       </c>
       <c r="E2">
-        <v>-8.44233654277928</v>
+        <v>-8.745979781941593</v>
       </c>
       <c r="F2">
-        <v>0.620687752908572</v>
+        <v>0.1430578858711891</v>
       </c>
       <c r="G2">
-        <v>-13.04774834714061</v>
+        <v>-13.5412000572239</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.336481202698565</v>
       </c>
       <c r="E3">
-        <v>-8.613811739553727</v>
+        <v>-8.123119881504589</v>
       </c>
       <c r="F3">
-        <v>1.034898116562182</v>
+        <v>0.2244302795123833</v>
       </c>
       <c r="G3">
-        <v>-12.96708028398518</v>
+        <v>-13.53171699952666</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.299166887158592</v>
       </c>
       <c r="E4">
-        <v>-10.07380534504867</v>
+        <v>-10.49004003346369</v>
       </c>
       <c r="F4">
-        <v>1.165495257467065</v>
+        <v>0.5580315957760411</v>
       </c>
       <c r="G4">
-        <v>-12.09913469668122</v>
+        <v>-12.49953524801946</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.254104044489215</v>
       </c>
       <c r="E5">
-        <v>-10.30906862669516</v>
+        <v>-11.01899749687765</v>
       </c>
       <c r="F5">
-        <v>1.048251924841168</v>
+        <v>0.5440181739832752</v>
       </c>
       <c r="G5">
-        <v>-11.80429088986265</v>
+        <v>-12.2246209253473</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.209337415320374</v>
       </c>
       <c r="E6">
-        <v>-11.16632687024319</v>
+        <v>-11.398823254271</v>
       </c>
       <c r="F6">
-        <v>1.407260635106221</v>
+        <v>0.6173572193684028</v>
       </c>
       <c r="G6">
-        <v>-10.92797955398095</v>
+        <v>-11.80692608411191</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.204366591146883</v>
       </c>
       <c r="E7">
-        <v>-11.40452007457264</v>
+        <v>-11.60716928641589</v>
       </c>
       <c r="F7">
-        <v>1.513829789862057</v>
+        <v>0.8176976013774084</v>
       </c>
       <c r="G7">
-        <v>-11.00599587015942</v>
+        <v>-11.71636611088515</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.24981924430091</v>
       </c>
       <c r="E8">
-        <v>-12.95830743371446</v>
+        <v>-13.36508666840147</v>
       </c>
       <c r="F8">
-        <v>1.357774576366484</v>
+        <v>0.9133787779645981</v>
       </c>
       <c r="G8">
-        <v>-10.74920678431477</v>
+        <v>-11.21881097960592</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.3530947037413248</v>
       </c>
       <c r="E9">
-        <v>-14.08833378064051</v>
+        <v>-13.50549200500929</v>
       </c>
       <c r="F9">
-        <v>1.41902598635202</v>
+        <v>1.220525870616755</v>
       </c>
       <c r="G9">
-        <v>-10.01324933711601</v>
+        <v>-10.26704237924762</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.4980575355882482</v>
       </c>
       <c r="E10">
-        <v>-14.89478707429648</v>
+        <v>-13.42397494439721</v>
       </c>
       <c r="F10">
-        <v>1.720405222060147</v>
+        <v>1.568798638481044</v>
       </c>
       <c r="G10">
-        <v>-8.6079657927874</v>
+        <v>-9.419880396839197</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.301178283286893</v>
       </c>
       <c r="E11">
-        <v>-15.72314459672756</v>
+        <v>-15.31747030969843</v>
       </c>
       <c r="F11">
-        <v>1.775027239083654</v>
+        <v>1.553102529153124</v>
       </c>
       <c r="G11">
-        <v>-8.499800338382792</v>
+        <v>-9.199828434843843</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.063010211088562</v>
       </c>
       <c r="E12">
-        <v>-15.74505335397667</v>
+        <v>-15.7227551479629</v>
       </c>
       <c r="F12">
-        <v>2.230816217841211</v>
+        <v>1.832995626706484</v>
       </c>
       <c r="G12">
-        <v>-8.248586211226277</v>
+        <v>-9.113320569357146</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.790302747268615</v>
       </c>
       <c r="E13">
-        <v>-16.78367245305789</v>
+        <v>-15.58693715552485</v>
       </c>
       <c r="F13">
-        <v>2.204778508885471</v>
+        <v>1.967697733344186</v>
       </c>
       <c r="G13">
-        <v>-7.364750005333812</v>
+        <v>-8.358837309320625</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.481541421040356</v>
       </c>
       <c r="E14">
-        <v>-17.91104511421544</v>
+        <v>-18.11054250814935</v>
       </c>
       <c r="F14">
-        <v>2.169865711979609</v>
+        <v>1.898998154438338</v>
       </c>
       <c r="G14">
-        <v>-6.991840224153688</v>
+        <v>-7.632043452174568</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.139347535466118</v>
       </c>
       <c r="E15">
-        <v>-18.64503829527468</v>
+        <v>-18.61325293621484</v>
       </c>
       <c r="F15">
-        <v>2.496424288037307</v>
+        <v>1.93441140241348</v>
       </c>
       <c r="G15">
-        <v>-5.915386547149808</v>
+        <v>-6.655753641006878</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.763844499267264</v>
       </c>
       <c r="E16">
-        <v>-18.80823544156311</v>
+        <v>-18.33841984868933</v>
       </c>
       <c r="F16">
-        <v>2.822981280389091</v>
+        <v>1.961478520214255</v>
       </c>
       <c r="G16">
-        <v>-5.509682501857664</v>
+        <v>-5.870558450002537</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>5.342281249345114</v>
       </c>
       <c r="E17">
-        <v>-19.87891613661863</v>
+        <v>-20.3571139348806</v>
       </c>
       <c r="F17">
-        <v>2.756391197762608</v>
+        <v>2.38258750683552</v>
       </c>
       <c r="G17">
-        <v>-5.942122512924962</v>
+        <v>-6.266930067419477</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>5.860663131713499</v>
       </c>
       <c r="E18">
-        <v>-20.88950851006638</v>
+        <v>-21.07162562075885</v>
       </c>
       <c r="F18">
-        <v>2.66446340419501</v>
+        <v>2.389658753747957</v>
       </c>
       <c r="G18">
-        <v>-4.858650479377828</v>
+        <v>-6.203552983615669</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.302647388681842</v>
       </c>
       <c r="E19">
-        <v>-22.61512881542924</v>
+        <v>-21.50609194552875</v>
       </c>
       <c r="F19">
-        <v>2.95187118631713</v>
+        <v>2.889305300421779</v>
       </c>
       <c r="G19">
-        <v>-4.55366316102693</v>
+        <v>-5.3923236624905</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.649735231207977</v>
       </c>
       <c r="E20">
-        <v>-22.08199609898022</v>
+        <v>-21.90147301113845</v>
       </c>
       <c r="F20">
-        <v>3.009456317108424</v>
+        <v>3.182490441723422</v>
       </c>
       <c r="G20">
-        <v>-4.407522438741343</v>
+        <v>-5.235784516666062</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.892584180225556</v>
       </c>
       <c r="E21">
-        <v>-22.44341360953239</v>
+        <v>-21.27267175280338</v>
       </c>
       <c r="F21">
-        <v>3.286174084301327</v>
+        <v>3.063264309291394</v>
       </c>
       <c r="G21">
-        <v>-4.481324430448316</v>
+        <v>-4.88480378913807</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>7.029188447153155</v>
       </c>
       <c r="E22">
-        <v>-24.54610636009195</v>
+        <v>-23.3092170835329</v>
       </c>
       <c r="F22">
-        <v>3.435846962957679</v>
+        <v>3.401567648417992</v>
       </c>
       <c r="G22">
-        <v>-3.900995729050694</v>
+        <v>-4.486730551313945</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>7.064289078868837</v>
       </c>
       <c r="E23">
-        <v>-23.63786655616556</v>
+        <v>-23.79648541523223</v>
       </c>
       <c r="F23">
-        <v>3.40098484464111</v>
+        <v>2.836105451310337</v>
       </c>
       <c r="G23">
-        <v>-3.780568013968626</v>
+        <v>-4.121411851055369</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.014054748351553</v>
       </c>
       <c r="E24">
-        <v>-23.68430605711422</v>
+        <v>-23.27703321876038</v>
       </c>
       <c r="F24">
-        <v>3.221227888415071</v>
+        <v>2.878829085791147</v>
       </c>
       <c r="G24">
-        <v>-3.528688467158717</v>
+        <v>-4.352365439511546</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>6.899803428627214</v>
       </c>
       <c r="E25">
-        <v>-23.57214934136625</v>
+        <v>-24.14683986378366</v>
       </c>
       <c r="F25">
-        <v>3.358734738229017</v>
+        <v>3.292101895542817</v>
       </c>
       <c r="G25">
-        <v>-3.727155672238025</v>
+        <v>-5.335640501767099</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>6.741394103588071</v>
       </c>
       <c r="E26">
-        <v>-24.08472731429446</v>
+        <v>-24.84721365380996</v>
       </c>
       <c r="F26">
-        <v>3.236916079213414</v>
+        <v>2.898831291503147</v>
       </c>
       <c r="G26">
-        <v>-3.943645487233125</v>
+        <v>-3.976356987706664</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.555151986390015</v>
       </c>
       <c r="E27">
-        <v>-24.34213936231247</v>
+        <v>-23.09483912400978</v>
       </c>
       <c r="F27">
-        <v>3.0998843411741</v>
+        <v>3.01113504537879</v>
       </c>
       <c r="G27">
-        <v>-3.11899852503729</v>
+        <v>-4.399153379618065</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.347922432427545</v>
       </c>
       <c r="E28">
-        <v>-23.71077498768906</v>
+        <v>-24.65882007814286</v>
       </c>
       <c r="F28">
-        <v>3.268229112573483</v>
+        <v>2.775131189860003</v>
       </c>
       <c r="G28">
-        <v>-3.411882488896612</v>
+        <v>-4.076438089904371</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.11665813863317</v>
       </c>
       <c r="E29">
-        <v>-24.11972788989974</v>
+        <v>-23.49621136073163</v>
       </c>
       <c r="F29">
-        <v>2.919769467411172</v>
+        <v>2.971273167487178</v>
       </c>
       <c r="G29">
-        <v>-3.776585427684883</v>
+        <v>-4.302429170597179</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.853919478849883</v>
       </c>
       <c r="E30">
-        <v>-23.60097307842507</v>
+        <v>-23.25320438853202</v>
       </c>
       <c r="F30">
-        <v>3.297429482242356</v>
+        <v>3.008599532208171</v>
       </c>
       <c r="G30">
-        <v>-3.343585934421447</v>
+        <v>-4.502611238265829</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.550755179627203</v>
       </c>
       <c r="E31">
-        <v>-24.01204530647135</v>
+        <v>-24.23317974921391</v>
       </c>
       <c r="F31">
-        <v>3.230760214320101</v>
+        <v>3.002023985247266</v>
       </c>
       <c r="G31">
-        <v>-2.983709771029434</v>
+        <v>-4.808869806103806</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.203122878210076</v>
       </c>
       <c r="E32">
-        <v>-23.84153467466054</v>
+        <v>-23.11038084680411</v>
       </c>
       <c r="F32">
-        <v>2.895088994424964</v>
+        <v>2.616258563540864</v>
       </c>
       <c r="G32">
-        <v>-3.858829310516997</v>
+        <v>-4.121421782691987</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.813440704752866</v>
       </c>
       <c r="E33">
-        <v>-23.00875283312397</v>
+        <v>-23.66350677599699</v>
       </c>
       <c r="F33">
-        <v>2.717571398363356</v>
+        <v>3.065896428522854</v>
       </c>
       <c r="G33">
-        <v>-4.020440212107599</v>
+        <v>-4.207757499810641</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.385310255514247</v>
       </c>
       <c r="E34">
-        <v>-23.11624974911805</v>
+        <v>-21.77678600781125</v>
       </c>
       <c r="F34">
-        <v>3.037518002224095</v>
+        <v>2.73470392895658</v>
       </c>
       <c r="G34">
-        <v>-4.037294199448028</v>
+        <v>-4.767491297408456</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.926618290478308</v>
       </c>
       <c r="E35">
-        <v>-21.60320054214924</v>
+        <v>-21.24675982453149</v>
       </c>
       <c r="F35">
-        <v>3.102643156878796</v>
+        <v>2.80173586553347</v>
       </c>
       <c r="G35">
-        <v>-3.580518368121547</v>
+        <v>-5.376032467891746</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.448202904502048</v>
       </c>
       <c r="E36">
-        <v>-22.4439524979393</v>
+        <v>-21.24864819819269</v>
       </c>
       <c r="F36">
-        <v>2.969822492868636</v>
+        <v>2.944937721819336</v>
       </c>
       <c r="G36">
-        <v>-4.645368583010281</v>
+        <v>-5.26518216105479</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.957024827000132</v>
       </c>
       <c r="E37">
-        <v>-21.27320158426228</v>
+        <v>-20.07774331639941</v>
       </c>
       <c r="F37">
-        <v>2.891063213987917</v>
+        <v>2.850290705194928</v>
       </c>
       <c r="G37">
-        <v>-4.126592854824329</v>
+        <v>-4.725225562508581</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.46204891397835</v>
       </c>
       <c r="E38">
-        <v>-20.08118948511924</v>
+        <v>-20.19100045133124</v>
       </c>
       <c r="F38">
-        <v>3.254278247164377</v>
+        <v>3.059990789164181</v>
       </c>
       <c r="G38">
-        <v>-4.074683500768557</v>
+        <v>-5.209819908001558</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.97635739476937</v>
       </c>
       <c r="E39">
-        <v>-19.75658846824943</v>
+        <v>-20.30653540868893</v>
       </c>
       <c r="F39">
-        <v>3.041136770240874</v>
+        <v>3.13370438099831</v>
       </c>
       <c r="G39">
-        <v>-4.64592144411534</v>
+        <v>-5.552249496401613</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.508336613090814</v>
       </c>
       <c r="E40">
-        <v>-18.26264489311898</v>
+        <v>-19.09246511265453</v>
       </c>
       <c r="F40">
-        <v>2.913138490743227</v>
+        <v>3.035462351945855</v>
       </c>
       <c r="G40">
-        <v>-4.289326031352743</v>
+        <v>-4.900767239728435</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.064651228254537</v>
       </c>
       <c r="E41">
-        <v>-18.61602436230754</v>
+        <v>-19.16490711135524</v>
       </c>
       <c r="F41">
-        <v>3.613480169551114</v>
+        <v>3.218812736894026</v>
       </c>
       <c r="G41">
-        <v>-4.53894447555933</v>
+        <v>-6.039677668876206</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.6528566813982046</v>
       </c>
       <c r="E42">
-        <v>-19.03106353358453</v>
+        <v>-18.6453462315072</v>
       </c>
       <c r="F42">
-        <v>3.559634168426172</v>
+        <v>2.988054115367175</v>
       </c>
       <c r="G42">
-        <v>-4.759281144471064</v>
+        <v>-5.415090284164068</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.2751623933628504</v>
       </c>
       <c r="E43">
-        <v>-17.36203556789552</v>
+        <v>-17.46875811483429</v>
       </c>
       <c r="F43">
-        <v>3.517574106723931</v>
+        <v>3.30571701529785</v>
       </c>
       <c r="G43">
-        <v>-4.909116435578477</v>
+        <v>-6.564637496129516</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.0665249558502707</v>
       </c>
       <c r="E44">
-        <v>-16.65420338117859</v>
+        <v>-17.02081052294355</v>
       </c>
       <c r="F44">
-        <v>3.659648364398004</v>
+        <v>2.839565848735572</v>
       </c>
       <c r="G44">
-        <v>-4.862086825647591</v>
+        <v>-5.859166862801905</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.3678045793163251</v>
       </c>
       <c r="E45">
-        <v>-16.78549289960897</v>
+        <v>-16.68103006120003</v>
       </c>
       <c r="F45">
-        <v>3.336713307474831</v>
+        <v>3.058517942662822</v>
       </c>
       <c r="G45">
-        <v>-5.505080843558076</v>
+        <v>-5.881863963019148</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.6296904239486347</v>
       </c>
       <c r="E46">
-        <v>-15.60080787141034</v>
+        <v>-15.93823805514389</v>
       </c>
       <c r="F46">
-        <v>3.311017678996826</v>
+        <v>3.041786089666204</v>
       </c>
       <c r="G46">
-        <v>-5.293682647602376</v>
+        <v>-6.524910949658262</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.8548657771264746</v>
       </c>
       <c r="E47">
-        <v>-15.6249265239752</v>
+        <v>-15.06916955138385</v>
       </c>
       <c r="F47">
-        <v>3.597072976267161</v>
+        <v>3.010880068726403</v>
       </c>
       <c r="G47">
-        <v>-5.355732202644935</v>
+        <v>-6.990403447389644</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.045824399555325</v>
       </c>
       <c r="E48">
-        <v>-14.32748249298558</v>
+        <v>-14.34955880377297</v>
       </c>
       <c r="F48">
-        <v>3.853275417031462</v>
+        <v>3.150494831113799</v>
       </c>
       <c r="G48">
-        <v>-5.558400490013579</v>
+        <v>-6.915664571295058</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.210888823310104</v>
       </c>
       <c r="E49">
-        <v>-14.21861797784118</v>
+        <v>-13.63539581039332</v>
       </c>
       <c r="F49">
-        <v>3.572622140638691</v>
+        <v>3.280447403711098</v>
       </c>
       <c r="G49">
-        <v>-6.11978624983549</v>
+        <v>-6.939497188632272</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.359246587914151</v>
       </c>
       <c r="E50">
-        <v>-13.39762375414658</v>
+        <v>-14.13581935908494</v>
       </c>
       <c r="F50">
-        <v>3.756927500253872</v>
+        <v>3.33815131244605</v>
       </c>
       <c r="G50">
-        <v>-6.327016468957249</v>
+        <v>-7.27514346922236</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.497989576404157</v>
       </c>
       <c r="E51">
-        <v>-13.06943165738868</v>
+        <v>-14.15198601129232</v>
       </c>
       <c r="F51">
-        <v>3.530585834525182</v>
+        <v>3.162040047237352</v>
       </c>
       <c r="G51">
-        <v>-6.277818451698139</v>
+        <v>-6.90312091424676</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.635502978924627</v>
       </c>
       <c r="E52">
-        <v>-12.76336568463227</v>
+        <v>-13.84205725020736</v>
       </c>
       <c r="F52">
-        <v>3.245881438400717</v>
+        <v>3.069562707717097</v>
       </c>
       <c r="G52">
-        <v>-6.608147996152158</v>
+        <v>-7.388413784848523</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.776534738190812</v>
       </c>
       <c r="E53">
-        <v>-12.10399269827142</v>
+        <v>-13.73091944111112</v>
       </c>
       <c r="F53">
-        <v>3.482590043051874</v>
+        <v>2.948942914079483</v>
       </c>
       <c r="G53">
-        <v>-6.048020243635169</v>
+        <v>-6.707520641604461</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.920937231265044</v>
       </c>
       <c r="E54">
-        <v>-10.49543797448084</v>
+        <v>-12.17044352585997</v>
       </c>
       <c r="F54">
-        <v>3.682456896992163</v>
+        <v>2.972207553977288</v>
       </c>
       <c r="G54">
-        <v>-6.653578612587576</v>
+        <v>-7.891580290816812</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.067777052086789</v>
       </c>
       <c r="E55">
-        <v>-11.55118376225906</v>
+        <v>-11.96386812705207</v>
       </c>
       <c r="F55">
-        <v>3.182218044305967</v>
+        <v>3.314687125602899</v>
       </c>
       <c r="G55">
-        <v>-6.601752022170285</v>
+        <v>-7.075272592834401</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.213356906369807</v>
       </c>
       <c r="E56">
-        <v>-11.08140892565136</v>
+        <v>-11.27122444215687</v>
       </c>
       <c r="F56">
-        <v>3.488623962589698</v>
+        <v>2.928877360130865</v>
       </c>
       <c r="G56">
-        <v>-6.854214224995107</v>
+        <v>-7.295655609383684</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.353558017230721</v>
       </c>
       <c r="E57">
-        <v>-9.910087424249367</v>
+        <v>-10.03933460090229</v>
       </c>
       <c r="F57">
-        <v>3.868488496055173</v>
+        <v>3.15478667414464</v>
       </c>
       <c r="G57">
-        <v>-7.310953640320656</v>
+        <v>-7.448642539844483</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.486640704368663</v>
       </c>
       <c r="E58">
-        <v>-10.24307064650738</v>
+        <v>-10.67648183683349</v>
       </c>
       <c r="F58">
-        <v>3.411261512326397</v>
+        <v>3.259222577032379</v>
       </c>
       <c r="G58">
-        <v>-7.576946042764478</v>
+        <v>-6.776681248465375</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.609323340506437</v>
       </c>
       <c r="E59">
-        <v>-10.86807704362401</v>
+        <v>-9.21484439527376</v>
       </c>
       <c r="F59">
-        <v>3.461919513443558</v>
+        <v>3.031811909810767</v>
       </c>
       <c r="G59">
-        <v>-6.745399903664802</v>
+        <v>-8.763803102957512</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.718105918621752</v>
       </c>
       <c r="E60">
-        <v>-10.07340231086199</v>
+        <v>-9.721512709621956</v>
       </c>
       <c r="F60">
-        <v>3.122103735167716</v>
+        <v>2.730518194222074</v>
       </c>
       <c r="G60">
-        <v>-7.232659238316892</v>
+        <v>-7.851860365436636</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.811221867495635</v>
       </c>
       <c r="E61">
-        <v>-9.636128332207333</v>
+        <v>-8.794828431062333</v>
       </c>
       <c r="F61">
-        <v>3.661279581490907</v>
+        <v>2.997112913203488</v>
       </c>
       <c r="G61">
-        <v>-7.68508832335031</v>
+        <v>-8.21809608680959</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.885428213898976</v>
       </c>
       <c r="E62">
-        <v>-8.740527499236359</v>
+        <v>-9.179916275252598</v>
       </c>
       <c r="F62">
-        <v>3.589002410922081</v>
+        <v>3.047101006718419</v>
       </c>
       <c r="G62">
-        <v>-7.331068515017267</v>
+        <v>-7.893699039961945</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.938179282845434</v>
       </c>
       <c r="E63">
-        <v>-8.352179153760572</v>
+        <v>-10.58092197832363</v>
       </c>
       <c r="F63">
-        <v>3.25167621834531</v>
+        <v>2.744052544975419</v>
       </c>
       <c r="G63">
-        <v>-7.672951863403342</v>
+        <v>-8.78834417704013</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.969273058957806</v>
       </c>
       <c r="E64">
-        <v>-7.913591917643689</v>
+        <v>-7.901478249673171</v>
       </c>
       <c r="F64">
-        <v>3.23715363510073</v>
+        <v>2.840482814460612</v>
       </c>
       <c r="G64">
-        <v>-7.888978202022944</v>
+        <v>-7.340649233807918</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.978828047136451</v>
       </c>
       <c r="E65">
-        <v>-8.144267855120409</v>
+        <v>-9.129084154516498</v>
       </c>
       <c r="F65">
-        <v>3.310455463396845</v>
+        <v>2.607964695661707</v>
       </c>
       <c r="G65">
-        <v>-7.881810870930422</v>
+        <v>-8.725096204512354</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.969257635478942</v>
       </c>
       <c r="E66">
-        <v>-8.553148301746974</v>
+        <v>-9.677070265710681</v>
       </c>
       <c r="F66">
-        <v>3.062006846794535</v>
+        <v>2.643517309757408</v>
       </c>
       <c r="G66">
-        <v>-7.89199741955476</v>
+        <v>-8.740424030359179</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.944673417216256</v>
       </c>
       <c r="E67">
-        <v>-8.72019012246791</v>
+        <v>-8.367064247823784</v>
       </c>
       <c r="F67">
-        <v>3.281517988909935</v>
+        <v>2.529077136601838</v>
       </c>
       <c r="G67">
-        <v>-8.021840326150516</v>
+        <v>-7.638565226886932</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.907369219264309</v>
       </c>
       <c r="E68">
-        <v>-7.777918836373885</v>
+        <v>-8.587849998067751</v>
       </c>
       <c r="F68">
-        <v>2.612351561047475</v>
+        <v>2.498567042140897</v>
       </c>
       <c r="G68">
-        <v>-8.265261429107586</v>
+        <v>-7.86264943334912</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.859387003625838</v>
       </c>
       <c r="E69">
-        <v>-8.716884336442311</v>
+        <v>-9.104173019000303</v>
       </c>
       <c r="F69">
-        <v>2.636796061852283</v>
+        <v>2.56982747351201</v>
       </c>
       <c r="G69">
-        <v>-7.967064039657734</v>
+        <v>-7.945469351105068</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.802275192501633</v>
       </c>
       <c r="E70">
-        <v>-8.133114223639518</v>
+        <v>-8.853712178584072</v>
       </c>
       <c r="F70">
-        <v>2.976820889308963</v>
+        <v>2.332634254850729</v>
       </c>
       <c r="G70">
-        <v>-8.337169788766095</v>
+        <v>-7.97871053886489</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.735108264168667</v>
       </c>
       <c r="E71">
-        <v>-8.31295351190613</v>
+        <v>-9.31792604911036</v>
       </c>
       <c r="F71">
-        <v>3.000335754741408</v>
+        <v>2.535644765033165</v>
       </c>
       <c r="G71">
-        <v>-7.345128401922552</v>
+        <v>-8.194776604030963</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.656290076906721</v>
       </c>
       <c r="E72">
-        <v>-9.01882486937774</v>
+        <v>-8.425603831320938</v>
       </c>
       <c r="F72">
-        <v>2.851172829389828</v>
+        <v>2.239865513442032</v>
       </c>
       <c r="G72">
-        <v>-7.996868881147792</v>
+        <v>-7.695281493065727</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.562551969865921</v>
       </c>
       <c r="E73">
-        <v>-8.14891406945228</v>
+        <v>-9.392079810985962</v>
       </c>
       <c r="F73">
-        <v>2.740796445613276</v>
+        <v>2.279646622331956</v>
       </c>
       <c r="G73">
-        <v>-7.56608083230459</v>
+        <v>-8.280820993142161</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.447921234126445</v>
       </c>
       <c r="E74">
-        <v>-8.428067321181111</v>
+        <v>-9.676680816946021</v>
       </c>
       <c r="F74">
-        <v>2.560147862956844</v>
+        <v>2.283243218465919</v>
       </c>
       <c r="G74">
-        <v>-8.143161888528185</v>
+        <v>-7.887101122702178</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.308341008010587</v>
       </c>
       <c r="E75">
-        <v>-8.788705934203962</v>
+        <v>-9.469113682330443</v>
       </c>
       <c r="F75">
-        <v>2.673053425080353</v>
+        <v>2.026296435921361</v>
       </c>
       <c r="G75">
-        <v>-7.407287204967908</v>
+        <v>-6.885796829439753</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.140790540559883</v>
       </c>
       <c r="E76">
-        <v>-9.493685182296062</v>
+        <v>-10.22227589386415</v>
       </c>
       <c r="F76">
-        <v>2.392379560510682</v>
+        <v>1.763060757186593</v>
       </c>
       <c r="G76">
-        <v>-6.794611163106068</v>
+        <v>-7.073647114974619</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.941072684768324</v>
       </c>
       <c r="E77">
-        <v>-10.8725557044176</v>
+        <v>-10.68316586446881</v>
       </c>
       <c r="F77">
-        <v>2.383890896803926</v>
+        <v>2.263364541815323</v>
       </c>
       <c r="G77">
-        <v>-7.176946067436497</v>
+        <v>-7.368444574155639</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.70754731430152</v>
       </c>
       <c r="E78">
-        <v>-9.514221811920846</v>
+        <v>-11.08488226521524</v>
       </c>
       <c r="F78">
-        <v>2.464351075837828</v>
+        <v>1.828524824907198</v>
       </c>
       <c r="G78">
-        <v>-6.904749702652081</v>
+        <v>-6.987132628396845</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.439625560927803</v>
       </c>
       <c r="E79">
-        <v>-10.51883659967847</v>
+        <v>-11.26838961742807</v>
       </c>
       <c r="F79">
-        <v>2.201918336002187</v>
+        <v>1.759381808345027</v>
       </c>
       <c r="G79">
-        <v>-6.956834515621435</v>
+        <v>-6.567464702020054</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.135045579677841</v>
       </c>
       <c r="E80">
-        <v>-11.36277207269593</v>
+        <v>-12.04681618545057</v>
       </c>
       <c r="F80">
-        <v>1.984247460160528</v>
+        <v>1.952440310554842</v>
       </c>
       <c r="G80">
-        <v>-7.186073241488268</v>
+        <v>-7.395577805395506</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.7946448705327516</v>
       </c>
       <c r="E81">
-        <v>-12.82541936395937</v>
+        <v>-11.97659766748763</v>
       </c>
       <c r="F81">
-        <v>2.222698141318669</v>
+        <v>1.635330123988656</v>
       </c>
       <c r="G81">
-        <v>-6.641395805003058</v>
+        <v>-5.913502846737963</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.4212497731427227</v>
       </c>
       <c r="E82">
-        <v>-13.30950870690533</v>
+        <v>-12.63405058086923</v>
       </c>
       <c r="F82">
-        <v>2.157151720890461</v>
+        <v>1.865205037614691</v>
       </c>
       <c r="G82">
-        <v>-6.378644426642182</v>
+        <v>-6.381147199069872</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.01733192986268</v>
       </c>
       <c r="E83">
-        <v>-13.73059791945657</v>
+        <v>-13.99507438692654</v>
       </c>
       <c r="F83">
-        <v>2.10111070336672</v>
+        <v>1.369034725425259</v>
       </c>
       <c r="G83">
-        <v>-5.884512399450565</v>
+        <v>-6.1231001059203</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.4093130565118167</v>
       </c>
       <c r="E84">
-        <v>-14.46766140589301</v>
+        <v>-16.104202099051</v>
       </c>
       <c r="F84">
-        <v>2.016654834308166</v>
+        <v>1.786387161615101</v>
       </c>
       <c r="G84">
-        <v>-5.8790864153117</v>
+        <v>-6.601626221439793</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.8468074871059832</v>
       </c>
       <c r="E85">
-        <v>-15.27686348327165</v>
+        <v>-15.81583793119056</v>
       </c>
       <c r="F85">
-        <v>1.635721299349769</v>
+        <v>1.517646521118265</v>
       </c>
       <c r="G85">
-        <v>-5.73840809316591</v>
+        <v>-6.377734026618883</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.283383866474208</v>
       </c>
       <c r="E86">
-        <v>-17.04849308455244</v>
+        <v>-16.49892200745558</v>
       </c>
       <c r="F86">
-        <v>1.798413824336948</v>
+        <v>1.330799313508804</v>
       </c>
       <c r="G86">
-        <v>-5.329519303064987</v>
+        <v>-5.530555491482769</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.703920113371759</v>
       </c>
       <c r="E87">
-        <v>-18.00440866283158</v>
+        <v>-19.29858313558766</v>
       </c>
       <c r="F87">
-        <v>1.618333792104159</v>
+        <v>1.121389047722077</v>
       </c>
       <c r="G87">
-        <v>-4.564068205656859</v>
+        <v>-5.797464915040969</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.092733276461117</v>
       </c>
       <c r="E88">
-        <v>-20.05306766153161</v>
+        <v>-21.11897534498305</v>
       </c>
       <c r="F88">
-        <v>1.813780522834457</v>
+        <v>1.022190460296696</v>
       </c>
       <c r="G88">
-        <v>-4.571722186943655</v>
+        <v>-4.803354437235381</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.43746803715742</v>
       </c>
       <c r="E89">
-        <v>-21.11022180472622</v>
+        <v>-21.35217364248204</v>
       </c>
       <c r="F89">
-        <v>1.770269786513674</v>
+        <v>0.9780446579038216</v>
       </c>
       <c r="G89">
-        <v>-4.13363107464082</v>
+        <v>-5.158195260862163</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.725041812536685</v>
       </c>
       <c r="E90">
-        <v>-22.31809261984412</v>
+        <v>-23.31452445506989</v>
       </c>
       <c r="F90">
-        <v>1.625897571556298</v>
+        <v>1.13203155147383</v>
       </c>
       <c r="G90">
-        <v>-4.339398032634221</v>
+        <v>-4.736299337337443</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.942924678782132</v>
       </c>
       <c r="E91">
-        <v>-24.3767550176271</v>
+        <v>-24.84117266948373</v>
       </c>
       <c r="F91">
-        <v>1.426930262575979</v>
+        <v>0.7589658675033365</v>
       </c>
       <c r="G91">
-        <v>-4.402583104796751</v>
+        <v>-4.514982746946085</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.082459939839918</v>
       </c>
       <c r="E92">
-        <v>-26.23118323766414</v>
+        <v>-27.24415305996591</v>
       </c>
       <c r="F92">
-        <v>1.420802904389143</v>
+        <v>0.567177497437704</v>
       </c>
       <c r="G92">
-        <v>-4.228057765057452</v>
+        <v>-4.235681951434393</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.136606392651424</v>
       </c>
       <c r="E93">
-        <v>-28.83291835234298</v>
+        <v>-27.69805106670273</v>
       </c>
       <c r="F93">
-        <v>1.297576330814715</v>
+        <v>0.7153062628265018</v>
       </c>
       <c r="G93">
-        <v>-4.23133520514133</v>
+        <v>-4.111576220258195</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.10142603327628</v>
       </c>
       <c r="E94">
-        <v>-30.27721853116434</v>
+        <v>-30.65592122700379</v>
       </c>
       <c r="F94">
-        <v>0.9905163419879073</v>
+        <v>0.4629110510829171</v>
       </c>
       <c r="G94">
-        <v>-4.36224741794627</v>
+        <v>-4.262163005203024</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.981065081396106</v>
       </c>
       <c r="E95">
-        <v>-32.84296586290422</v>
+        <v>-31.79853446743416</v>
       </c>
       <c r="F95">
-        <v>1.000720159201083</v>
+        <v>0.547013753722329</v>
       </c>
       <c r="G95">
-        <v>-3.938073839090531</v>
+        <v>-4.617324951747115</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.782031894797361</v>
       </c>
       <c r="E96">
-        <v>-35.1553224315449</v>
+        <v>-35.35624403055422</v>
       </c>
       <c r="F96">
-        <v>1.063586949220368</v>
+        <v>0.05781966609040713</v>
       </c>
       <c r="G96">
-        <v>-4.306140292146702</v>
+        <v>-3.775036092372504</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.524033204879353</v>
       </c>
       <c r="E97">
-        <v>-37.11355459702277</v>
+        <v>-37.33690119931807</v>
       </c>
       <c r="F97">
-        <v>0.5744641283546409</v>
+        <v>0.5114342166260663</v>
       </c>
       <c r="G97">
-        <v>-4.660686477220489</v>
+        <v>-4.349154210338453</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.219180636614308</v>
       </c>
       <c r="E98">
-        <v>-40.06273461570311</v>
+        <v>-39.17699000640983</v>
       </c>
       <c r="F98">
-        <v>0.6363157628821285</v>
+        <v>0.1679521591559817</v>
       </c>
       <c r="G98">
-        <v>-4.909821581778342</v>
+        <v>-4.706206478385468</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.899391934394174</v>
       </c>
       <c r="E99">
-        <v>-42.15687987157318</v>
+        <v>-42.53542407082237</v>
       </c>
       <c r="F99">
-        <v>0.4927100615878257</v>
+        <v>0.3460002966992616</v>
       </c>
       <c r="G99">
-        <v>-4.829302493172189</v>
+        <v>-4.094675885280216</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.565017636893424</v>
       </c>
       <c r="E100">
-        <v>-45.78992965675886</v>
+        <v>-44.78498881887269</v>
       </c>
       <c r="F100">
-        <v>0.565425918695228</v>
+        <v>-0.5358530844889704</v>
       </c>
       <c r="G100">
-        <v>-4.881195294500264</v>
+        <v>-5.22039710099953</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.263935130087122</v>
       </c>
       <c r="E101">
-        <v>-46.92339311545673</v>
+        <v>-46.63766451946876</v>
       </c>
       <c r="F101">
-        <v>0.2851440213396277</v>
+        <v>-0.711870911048657</v>
       </c>
       <c r="G101">
-        <v>-5.17510552747676</v>
+        <v>-5.37456589621785</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.9546589360913939</v>
       </c>
       <c r="E102">
-        <v>-49.9414274493052</v>
+        <v>-50.53487604318089</v>
       </c>
       <c r="F102">
-        <v>0.1304959305499234</v>
+        <v>-0.9299020799860789</v>
       </c>
       <c r="G102">
-        <v>-5.148468878067784</v>
+        <v>-4.254879805016627</v>
       </c>
     </row>
   </sheetData>
